--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.96917142243062</v>
+        <v>11.36999035614498</v>
       </c>
       <c r="D2" t="n">
-        <v>69.85863165832461</v>
+        <v>11.35202764447775</v>
       </c>
       <c r="E2" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F2" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.207419042658</v>
+        <v>8.646205594431926</v>
       </c>
       <c r="D3" t="n">
-        <v>52.11314365947912</v>
+        <v>8.468385844665358</v>
       </c>
       <c r="E3" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F3" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.43749214285091</v>
+        <v>6.246092473213273</v>
       </c>
       <c r="D4" t="n">
-        <v>37.15709640057113</v>
+        <v>6.038028165092808</v>
       </c>
       <c r="E4" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F4" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.65312859494544</v>
+        <v>8.393633396678634</v>
       </c>
       <c r="D5" t="n">
-        <v>50.7005029739782</v>
+        <v>8.238831733271457</v>
       </c>
       <c r="E5" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F5" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.46781064886834</v>
+        <v>5.763519230441106</v>
       </c>
       <c r="D6" t="n">
-        <v>34.38142916092005</v>
+        <v>5.586982238649508</v>
       </c>
       <c r="E6" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F6" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.19292840575206</v>
+        <v>9.781350865934709</v>
       </c>
       <c r="D7" t="n">
-        <v>60.15702860269558</v>
+        <v>9.775517147938032</v>
       </c>
       <c r="E7" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F7" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.14900669616774</v>
+        <v>2.949213588127257</v>
       </c>
       <c r="D8" t="n">
-        <v>17.99214665604964</v>
+        <v>2.923723831608067</v>
       </c>
       <c r="E8" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F8" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.69728497277415</v>
+        <v>6.7758088080758</v>
       </c>
       <c r="D9" t="n">
-        <v>40.95264851759591</v>
+        <v>6.654805384109336</v>
       </c>
       <c r="E9" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F9" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.8923508369261</v>
+        <v>3.232507011000491</v>
       </c>
       <c r="D10" t="n">
-        <v>18.92429968097077</v>
+        <v>3.075198698157751</v>
       </c>
       <c r="E10" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F10" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.06990529948539</v>
+        <v>3.098859611166376</v>
       </c>
       <c r="D11" t="n">
-        <v>18.91279411565384</v>
+        <v>3.073329043793749</v>
       </c>
       <c r="E11" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F11" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.735548788075215</v>
+        <v>1.419526678062223</v>
       </c>
       <c r="D12" t="n">
-        <v>8.548049957808225</v>
+        <v>1.389058118143837</v>
       </c>
       <c r="E12" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F12" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55.06871350861939</v>
+        <v>8.948665945150651</v>
       </c>
       <c r="D13" t="n">
-        <v>55.05493863356849</v>
+        <v>8.94642752795488</v>
       </c>
       <c r="E13" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F13" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.40443068247831</v>
+        <v>2.665719985902725</v>
       </c>
       <c r="D14" t="n">
-        <v>16.31626369996646</v>
+        <v>2.651392851244549</v>
       </c>
       <c r="E14" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F14" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.79391662074891</v>
+        <v>4.679011450871698</v>
       </c>
       <c r="D15" t="n">
-        <v>28.75878580250359</v>
+        <v>4.673302692906833</v>
       </c>
       <c r="E15" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F15" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>6.700042538829489</v>
+        <v>1.088756912559792</v>
       </c>
       <c r="D16" t="n">
-        <v>6.556868106429243</v>
+        <v>1.065491067294752</v>
       </c>
       <c r="E16" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F16" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5.159628766212765</v>
+        <v>0.8384396745095744</v>
       </c>
       <c r="D17" t="n">
-        <v>5.216620185849636</v>
+        <v>0.8477007802005658</v>
       </c>
       <c r="E17" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F17" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>5.368675356543625</v>
+        <v>0.8724097454383392</v>
       </c>
       <c r="D18" t="n">
-        <v>6.588468746917624</v>
+        <v>1.070626171374114</v>
       </c>
       <c r="E18" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F18" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>5.308517317026495</v>
+        <v>0.8626340640168054</v>
       </c>
       <c r="D19" t="n">
-        <v>5.129510336425308</v>
+        <v>0.8335454296691126</v>
       </c>
       <c r="E19" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F19" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>12.34604046513976</v>
+        <v>2.006231575585211</v>
       </c>
       <c r="D20" t="n">
-        <v>12.5377512428797</v>
+        <v>2.037384576967951</v>
       </c>
       <c r="E20" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F20" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>49.52979688144851</v>
+        <v>8.048591993235384</v>
       </c>
       <c r="D21" t="n">
-        <v>49.57632686731917</v>
+        <v>8.056153115939367</v>
       </c>
       <c r="E21" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F21" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>14.05269783885526</v>
+        <v>2.28356339881398</v>
       </c>
       <c r="D22" t="n">
-        <v>15.24459099699778</v>
+        <v>2.47724603701214</v>
       </c>
       <c r="E22" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F22" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>33.48467975711215</v>
+        <v>5.441260460530724</v>
       </c>
       <c r="D23" t="n">
-        <v>33.58002529773467</v>
+        <v>5.456754110881884</v>
       </c>
       <c r="E23" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F23" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>43.8504673024598</v>
+        <v>7.125700936649719</v>
       </c>
       <c r="D24" t="n">
-        <v>44.13819248984611</v>
+        <v>7.172456279599993</v>
       </c>
       <c r="E24" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F24" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>31.47377056380761</v>
+        <v>5.114487716618737</v>
       </c>
       <c r="D25" t="n">
-        <v>32.7956629037865</v>
+        <v>5.329295221865307</v>
       </c>
       <c r="E25" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F25" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>48.79566903404874</v>
+        <v>7.92929621803292</v>
       </c>
       <c r="D26" t="n">
-        <v>48.91581895700799</v>
+        <v>7.948820580513798</v>
       </c>
       <c r="E26" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F26" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>47.76877019173048</v>
+        <v>7.762425156156202</v>
       </c>
       <c r="D27" t="n">
-        <v>48.67293696818621</v>
+        <v>7.909352257330259</v>
       </c>
       <c r="E27" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F27" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>35.00261348291614</v>
+        <v>5.687924690973873</v>
       </c>
       <c r="D28" t="n">
-        <v>36.18708676110823</v>
+        <v>5.880401598680087</v>
       </c>
       <c r="E28" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F28" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>41.19606326154869</v>
+        <v>6.694360280001663</v>
       </c>
       <c r="D29" t="n">
-        <v>41.38378400928214</v>
+        <v>6.724864901508347</v>
       </c>
       <c r="E29" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F29" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>41.34310394618537</v>
+        <v>6.718254391255122</v>
       </c>
       <c r="D30" t="n">
-        <v>42.66283070177213</v>
+        <v>6.932709989037972</v>
       </c>
       <c r="E30" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F30" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>34.983958590311</v>
+        <v>5.684893270925539</v>
       </c>
       <c r="D31" t="n">
-        <v>34.94315996675805</v>
+        <v>5.678263494598182</v>
       </c>
       <c r="E31" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F31" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>59.85138921089321</v>
+        <v>9.725850746770147</v>
       </c>
       <c r="D32" t="n">
-        <v>61.19701217199835</v>
+        <v>9.944514477949731</v>
       </c>
       <c r="E32" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F32" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>38.58759846898279</v>
+        <v>6.270484751209704</v>
       </c>
       <c r="D33" t="n">
-        <v>38.79802852513706</v>
+        <v>6.304679635334773</v>
       </c>
       <c r="E33" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F33" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>18.25446977232057</v>
+        <v>2.966351338002093</v>
       </c>
       <c r="D34" t="n">
-        <v>18.54031421099313</v>
+        <v>3.012801059286384</v>
       </c>
       <c r="E34" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F34" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>2.128294620579561</v>
+        <v>0.3458478758441787</v>
       </c>
       <c r="D35" t="n">
-        <v>2.165942552060976</v>
+        <v>0.3519656647099086</v>
       </c>
       <c r="E35" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F35" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>24.13414055761898</v>
+        <v>3.921797840613085</v>
       </c>
       <c r="D36" t="n">
-        <v>24.27753697672781</v>
+        <v>3.945099758718269</v>
       </c>
       <c r="E36" t="n">
-        <v>18.26440554371086</v>
+        <v>2.967965900853015</v>
       </c>
       <c r="F36" t="n">
-        <v>18.23827788822702</v>
+        <v>2.96372015683689</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
